--- a/tests/runners/bolts/geometries/M12_bolt.xlsx
+++ b/tests/runners/bolts/geometries/M12_bolt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\laghida\Documents\GitLab\cassy\tests\bolts\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\laghida\Documents\GitLab\cassy\tests\runners\bolts\geometries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D5AB07-7B05-4809-AFD4-5E13714268A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A414C679-422D-4EB1-A10D-489ECEFE68F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F09436F1-1F29-42A5-B1F9-53A78950820F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
   <si>
     <t>Dimensions of the bolts and assembled parts</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>material</t>
+  </si>
+  <si>
+    <t>venting hole</t>
+  </si>
+  <si>
+    <t>d_vh</t>
   </si>
 </sst>
 </file>
@@ -337,7 +343,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -640,11 +646,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -749,6 +797,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -818,14 +878,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>107008</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>34685</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>168954</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>117461</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>125625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -862,13 +922,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>678181</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>125730</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>207186</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -906,14 +966,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>510541</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>156101</xdr:rowOff>
+      <xdr:colOff>515983</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>164265</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1246,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A35CF97-1329-4AF8-AE95-32CC01118615}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.53515625" style="2" customWidth="1"/>
@@ -1546,7 +1606,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="24" t="s">
         <v>33</v>
       </c>
@@ -1567,18 +1627,18 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
-      <c r="A16" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="16">
-        <v>4</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>29</v>
+    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="38">
+        <v>0</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>7</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1588,17 +1648,17 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="18">
-        <v>0.15</v>
-      </c>
-      <c r="D17" s="5" t="s">
+    <row r="17" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+      <c r="A17" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="16">
+        <v>4</v>
+      </c>
+      <c r="D17" s="28" t="s">
         <v>29</v>
       </c>
       <c r="E17" s="1"/>
@@ -1609,17 +1669,17 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="21">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="18">
         <v>0.15</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E18" s="1"/>
@@ -1632,13 +1692,13 @@
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="19" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>39</v>
+        <v>32</v>
+      </c>
+      <c r="C19" s="21">
+        <v>0.15</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>29</v>
@@ -1651,11 +1711,19 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>29</v>
+      </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1716,6 +1784,19 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
@@ -1727,15 +1808,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="71e126cb-1963-4e7b-b13a-15d2f64f78e9">
@@ -1744,6 +1816,15 @@
     <TaxCatchAll xmlns="f41f4605-e15c-4135-bd96-d3970596b173" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1976,14 +2057,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F460EF5-1FE2-485A-B28D-6307C5242F38}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B53875E3-DFDB-4F02-8AAC-AEAA1E089733}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1992,6 +2065,14 @@
     <ds:schemaRef ds:uri="cfb58fdf-baa4-49ab-9b9a-8c103073e122"/>
     <ds:schemaRef ds:uri="71e126cb-1963-4e7b-b13a-15d2f64f78e9"/>
     <ds:schemaRef ds:uri="f41f4605-e15c-4135-bd96-d3970596b173"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F460EF5-1FE2-485A-B28D-6307C5242F38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/tests/runners/bolts/geometries/M12_bolt.xlsx
+++ b/tests/runners/bolts/geometries/M12_bolt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\laghida\Documents\GitLab\cassy\tests\runners\bolts\geometries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A414C679-422D-4EB1-A10D-489ECEFE68F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67637075-426D-4282-83E6-CAEC54D40AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F09436F1-1F29-42A5-B1F9-53A78950820F}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{F09436F1-1F29-42A5-B1F9-53A78950820F}"/>
   </bookViews>
   <sheets>
     <sheet name="Bolt Data" sheetId="1" r:id="rId1"/>
@@ -240,9 +240,6 @@
     <t>Material name</t>
   </si>
   <si>
-    <t>SS660 (non leak-tight)</t>
-  </si>
-  <si>
     <t>fatigue stress coefficient (RB 3285.11)</t>
   </si>
   <si>
@@ -253,6 +250,9 @@
   </si>
   <si>
     <t>d_vh</t>
+  </si>
+  <si>
+    <t>Inconel 718 (non leak tight) SDC-IC</t>
   </si>
 </sst>
 </file>
@@ -790,6 +790,18 @@
     <xf numFmtId="2" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,18 +809,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1307,22 +1307,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A35CF97-1329-4AF8-AE95-32CC01118615}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.53515625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="44" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.69140625" style="2" customWidth="1"/>
-    <col min="4" max="11" width="11.15234375" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.84375" style="2"/>
+    <col min="3" max="3" width="26.7109375" style="2" customWidth="1"/>
+    <col min="4" max="11" width="11.140625" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="35"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1331,7 +1331,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -1352,7 +1352,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
@@ -1373,7 +1373,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1394,7 +1394,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -1415,7 +1415,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1437,7 +1437,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -1458,7 +1458,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -1479,7 +1479,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -1501,7 +1501,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>36</v>
       </c>
@@ -1522,7 +1522,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -1543,7 +1543,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -1585,7 +1585,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>26</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
         <v>33</v>
       </c>
@@ -1627,17 +1627,17 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="37" t="s">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="38">
+      <c r="B16" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="35">
         <v>0</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="36" t="s">
         <v>7</v>
       </c>
       <c r="E16" s="1"/>
@@ -1648,12 +1648,12 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="16">
         <v>4</v>
@@ -1669,7 +1669,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
@@ -1690,7 +1690,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>34</v>
       </c>
@@ -1711,15 +1711,15 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="20" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>29</v>
@@ -1732,7 +1732,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1745,7 +1745,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1758,7 +1758,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1771,7 +1771,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1784,7 +1784,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
